--- a/05_Machine_Learning/01_DataEngineering/GraduationProjects/FactoryTwo/OldSystem/Job change.xlsx
+++ b/05_Machine_Learning/01_DataEngineering/GraduationProjects/FactoryTwo/OldSystem/Job change.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kandilglass20-my.sharepoint.com/personal/ahmed_fergany_kandilglass_com/Documents/Attachments/GitHub/Final_Learning_AI/05_Machine_Learning/01_DataEngineering/GraduationProjects/FactoryTwo/OldSystem/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="312" documentId="11_F25DC773A252ABDACC10481B095D43B45BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5B6866E-3535-44EB-9E0E-C911AA792C24}"/>
+  <xr:revisionPtr revIDLastSave="315" documentId="11_F25DC773A252ABDACC10481B095D43B45BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE0C61A1-7E37-42A7-A679-068CD64AB8AB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -488,7 +488,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -548,9 +548,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -582,6 +579,27 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -940,7 +958,7 @@
       <c r="M2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="32" t="s">
         <v>12</v>
       </c>
       <c r="O2" s="9" t="s">
@@ -964,7 +982,7 @@
       <c r="U2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="V2" s="13" t="s">
+      <c r="V2" s="34" t="s">
         <v>79</v>
       </c>
       <c r="W2" s="13" t="s">
@@ -976,7 +994,7 @@
       <c r="Y2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="Z2" s="14" t="s">
+      <c r="Z2" s="37" t="s">
         <v>23</v>
       </c>
       <c r="AA2" s="14" t="s">
@@ -1046,23 +1064,23 @@
       <c r="H3" s="19">
         <v>0.35416666666666669</v>
       </c>
-      <c r="I3" s="29">
+      <c r="I3" s="28">
         <v>5</v>
       </c>
-      <c r="J3" s="29">
+      <c r="J3" s="28">
         <v>0</v>
       </c>
       <c r="K3" s="20">
         <f>H3+(I3/24)+(J3/24)</f>
         <v>0.5625</v>
       </c>
-      <c r="L3" s="29">
+      <c r="L3" s="28">
         <v>1</v>
       </c>
-      <c r="M3" s="29">
-        <v>0</v>
-      </c>
-      <c r="N3" s="21"/>
+      <c r="M3" s="28">
+        <v>0</v>
+      </c>
+      <c r="N3" s="33"/>
       <c r="O3" s="20">
         <f>K3+(L3/24)</f>
         <v>0.60416666666666663</v>
@@ -1071,7 +1089,7 @@
         <f>K3+(L3/24)+(M3/24)</f>
         <v>0.60416666666666663</v>
       </c>
-      <c r="Q3" s="29">
+      <c r="Q3" s="28">
         <v>0.7</v>
       </c>
       <c r="R3" s="20">
@@ -1086,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="U3" s="20"/>
-      <c r="V3" s="20"/>
+      <c r="V3" s="35"/>
       <c r="W3" s="18"/>
       <c r="X3" s="20">
         <v>0.63541666666666663</v>
@@ -1095,7 +1113,7 @@
         <f t="shared" ref="Y3:Y12" si="0">X3-S3</f>
         <v>2.0833333333333259E-3</v>
       </c>
-      <c r="Z3" s="20"/>
+      <c r="Z3" s="35"/>
       <c r="AA3" s="20">
         <v>0.72</v>
       </c>
@@ -1153,7 +1171,7 @@
       </c>
     </row>
     <row r="4" spans="1:40" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="22">
+      <c r="A4" s="21">
         <f t="shared" ref="A4:A12" si="1">MONTH(B4)</f>
         <v>6</v>
       </c>
@@ -1176,23 +1194,23 @@
       <c r="H4" s="6">
         <v>0.35416666666666669</v>
       </c>
-      <c r="I4" s="30">
-        <v>0</v>
-      </c>
-      <c r="J4" s="30">
+      <c r="I4" s="29">
+        <v>0</v>
+      </c>
+      <c r="J4" s="29">
         <v>1.25</v>
       </c>
       <c r="K4" s="20">
         <f t="shared" ref="K4:K12" si="2">H4+(I4/24)+(J4/24)</f>
         <v>0.40625</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="29">
         <v>3</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="29">
         <v>0.5</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N4" s="15" t="s">
         <v>46</v>
       </c>
       <c r="O4" s="20">
@@ -1203,7 +1221,7 @@
         <f t="shared" ref="P4:P12" si="4">K4+(L4/24)+(M4/24)</f>
         <v>0.55208333333333337</v>
       </c>
-      <c r="Q4" s="30">
+      <c r="Q4" s="29">
         <v>1.5</v>
       </c>
       <c r="R4" s="20">
@@ -1220,7 +1238,7 @@
       <c r="U4" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="V4" s="7" t="s">
+      <c r="V4" s="36" t="s">
         <v>48</v>
       </c>
       <c r="W4" s="4"/>
@@ -1231,7 +1249,7 @@
         <f t="shared" si="0"/>
         <v>2.0833333333333259E-2</v>
       </c>
-      <c r="Z4" s="7" t="s">
+      <c r="Z4" s="36" t="s">
         <v>49</v>
       </c>
       <c r="AA4" s="7">
@@ -1291,7 +1309,7 @@
       </c>
     </row>
     <row r="5" spans="1:40" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22">
+      <c r="A5" s="21">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -1314,23 +1332,23 @@
       <c r="H5" s="6">
         <v>0.35416666666666669</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="29">
         <v>8</v>
       </c>
-      <c r="J5" s="30">
+      <c r="J5" s="29">
         <v>0</v>
       </c>
       <c r="K5" s="20">
         <f t="shared" si="2"/>
         <v>0.6875</v>
       </c>
-      <c r="L5" s="30">
+      <c r="L5" s="29">
         <v>2</v>
       </c>
-      <c r="M5" s="30">
-        <v>0</v>
-      </c>
-      <c r="N5" s="8"/>
+      <c r="M5" s="29">
+        <v>0</v>
+      </c>
+      <c r="N5" s="15"/>
       <c r="O5" s="20">
         <f t="shared" si="3"/>
         <v>0.77083333333333337</v>
@@ -1339,7 +1357,7 @@
         <f t="shared" si="4"/>
         <v>0.77083333333333337</v>
       </c>
-      <c r="Q5" s="30">
+      <c r="Q5" s="29">
         <v>1</v>
       </c>
       <c r="R5" s="20">
@@ -1354,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
+      <c r="V5" s="36"/>
       <c r="W5" s="4"/>
       <c r="X5" s="7">
         <v>0.81944444444444442</v>
@@ -1363,7 +1381,7 @@
         <f t="shared" si="0"/>
         <v>6.9444444444444198E-3</v>
       </c>
-      <c r="Z5" s="7"/>
+      <c r="Z5" s="36"/>
       <c r="AA5" s="7">
         <v>0.58304398148148151</v>
       </c>
@@ -1421,7 +1439,7 @@
       </c>
     </row>
     <row r="6" spans="1:40" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22">
+      <c r="A6" s="21">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -1444,23 +1462,23 @@
       <c r="H6" s="6">
         <v>0.35416666666666669</v>
       </c>
-      <c r="I6" s="30">
-        <v>0</v>
-      </c>
-      <c r="J6" s="30">
+      <c r="I6" s="29">
+        <v>0</v>
+      </c>
+      <c r="J6" s="29">
         <v>3</v>
       </c>
       <c r="K6" s="20">
         <f t="shared" si="2"/>
         <v>0.47916666666666669</v>
       </c>
-      <c r="L6" s="30">
+      <c r="L6" s="29">
         <v>1</v>
       </c>
-      <c r="M6" s="30">
+      <c r="M6" s="29">
         <v>1.3</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="15" t="s">
         <v>56</v>
       </c>
       <c r="O6" s="20">
@@ -1471,7 +1489,7 @@
         <f t="shared" si="4"/>
         <v>0.57500000000000007</v>
       </c>
-      <c r="Q6" s="30">
+      <c r="Q6" s="29">
         <v>0.7</v>
       </c>
       <c r="R6" s="20">
@@ -1488,7 +1506,7 @@
       <c r="U6" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="V6" s="7" t="s">
+      <c r="V6" s="36" t="s">
         <v>58</v>
       </c>
       <c r="W6" s="4"/>
@@ -1499,7 +1517,7 @@
         <f t="shared" si="0"/>
         <v>1.388888888888884E-3</v>
       </c>
-      <c r="Z6" s="7"/>
+      <c r="Z6" s="36"/>
       <c r="AA6" s="7">
         <v>0.77824074074074079</v>
       </c>
@@ -1557,7 +1575,7 @@
       </c>
     </row>
     <row r="7" spans="1:40" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22">
+      <c r="A7" s="21">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -1580,23 +1598,23 @@
       <c r="H7" s="6">
         <v>0.35416666666666669</v>
       </c>
-      <c r="I7" s="30">
-        <v>0</v>
-      </c>
-      <c r="J7" s="30">
+      <c r="I7" s="29">
+        <v>0</v>
+      </c>
+      <c r="J7" s="29">
         <v>1</v>
       </c>
       <c r="K7" s="20">
         <f t="shared" si="2"/>
         <v>0.39583333333333337</v>
       </c>
-      <c r="L7" s="30">
+      <c r="L7" s="29">
         <v>2</v>
       </c>
-      <c r="M7" s="30">
-        <v>0</v>
-      </c>
-      <c r="N7" s="8"/>
+      <c r="M7" s="29">
+        <v>0</v>
+      </c>
+      <c r="N7" s="15"/>
       <c r="O7" s="20">
         <f t="shared" si="3"/>
         <v>0.47916666666666669</v>
@@ -1605,7 +1623,7 @@
         <f t="shared" si="4"/>
         <v>0.47916666666666669</v>
       </c>
-      <c r="Q7" s="30">
+      <c r="Q7" s="29">
         <v>0.5</v>
       </c>
       <c r="R7" s="20">
@@ -1622,7 +1640,7 @@
       <c r="U7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="V7" s="7" t="s">
+      <c r="V7" s="36" t="s">
         <v>62</v>
       </c>
       <c r="W7" s="4"/>
@@ -1633,7 +1651,7 @@
         <f t="shared" si="0"/>
         <v>4.166666666666663E-2</v>
       </c>
-      <c r="Z7" s="7" t="s">
+      <c r="Z7" s="36" t="s">
         <v>49</v>
       </c>
       <c r="AA7" s="7">
@@ -1693,7 +1711,7 @@
       </c>
     </row>
     <row r="8" spans="1:40" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="22">
+      <c r="A8" s="21">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -1716,23 +1734,23 @@
       <c r="H8" s="6">
         <v>0.4375</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="29">
         <v>5</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="29">
         <v>0</v>
       </c>
       <c r="K8" s="20">
         <f t="shared" si="2"/>
         <v>0.64583333333333337</v>
       </c>
-      <c r="L8" s="30">
+      <c r="L8" s="29">
         <v>2</v>
       </c>
-      <c r="M8" s="30">
+      <c r="M8" s="29">
         <v>0.5</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="N8" s="15" t="s">
         <v>56</v>
       </c>
       <c r="O8" s="20">
@@ -1743,7 +1761,7 @@
         <f t="shared" si="4"/>
         <v>0.75000000000000011</v>
       </c>
-      <c r="Q8" s="30">
+      <c r="Q8" s="29">
         <v>1</v>
       </c>
       <c r="R8" s="20">
@@ -1760,7 +1778,7 @@
       <c r="U8" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="V8" s="7" t="s">
+      <c r="V8" s="36" t="s">
         <v>58</v>
       </c>
       <c r="W8" s="4"/>
@@ -1771,7 +1789,7 @@
         <f t="shared" si="0"/>
         <v>3.4722222222222099E-3</v>
       </c>
-      <c r="Z8" s="7"/>
+      <c r="Z8" s="36"/>
       <c r="AA8" s="7">
         <v>0.6864872685185186</v>
       </c>
@@ -1829,7 +1847,7 @@
       </c>
     </row>
     <row r="9" spans="1:40" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22">
+      <c r="A9" s="21">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -1852,23 +1870,23 @@
       <c r="H9" s="6">
         <v>0.4375</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="29">
         <v>6</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="29">
         <v>0</v>
       </c>
       <c r="K9" s="20">
         <f t="shared" si="2"/>
         <v>0.6875</v>
       </c>
-      <c r="L9" s="30">
+      <c r="L9" s="29">
         <v>2.5</v>
       </c>
-      <c r="M9" s="30">
+      <c r="M9" s="29">
         <v>0.5</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="N9" s="15" t="s">
         <v>56</v>
       </c>
       <c r="O9" s="20">
@@ -1879,7 +1897,7 @@
         <f t="shared" si="4"/>
         <v>0.8125</v>
       </c>
-      <c r="Q9" s="30">
+      <c r="Q9" s="29">
         <v>0.7</v>
       </c>
       <c r="R9" s="20">
@@ -1896,7 +1914,7 @@
       <c r="U9" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="V9" s="7" t="s">
+      <c r="V9" s="36" t="s">
         <v>58</v>
       </c>
       <c r="W9" s="4"/>
@@ -1907,7 +1925,7 @@
         <f t="shared" si="0"/>
         <v>4.1666666666666741E-2</v>
       </c>
-      <c r="Z9" s="7" t="s">
+      <c r="Z9" s="36" t="s">
         <v>49</v>
       </c>
       <c r="AA9" s="7">
@@ -1967,7 +1985,7 @@
       </c>
     </row>
     <row r="10" spans="1:40" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22">
+      <c r="A10" s="21">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -1990,23 +2008,23 @@
       <c r="H10" s="6">
         <v>0.4375</v>
       </c>
-      <c r="I10" s="30">
-        <v>0</v>
-      </c>
-      <c r="J10" s="30">
+      <c r="I10" s="29">
+        <v>0</v>
+      </c>
+      <c r="J10" s="29">
         <v>3</v>
       </c>
       <c r="K10" s="20">
         <f t="shared" si="2"/>
         <v>0.5625</v>
       </c>
-      <c r="L10" s="30">
+      <c r="L10" s="29">
         <v>5</v>
       </c>
-      <c r="M10" s="30">
+      <c r="M10" s="29">
         <v>0.5</v>
       </c>
-      <c r="N10" s="8" t="s">
+      <c r="N10" s="15" t="s">
         <v>56</v>
       </c>
       <c r="O10" s="20">
@@ -2017,7 +2035,7 @@
         <f t="shared" si="4"/>
         <v>0.79166666666666674</v>
       </c>
-      <c r="Q10" s="30">
+      <c r="Q10" s="29">
         <v>0.7</v>
       </c>
       <c r="R10" s="20">
@@ -2034,7 +2052,7 @@
       <c r="U10" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="V10" s="7" t="s">
+      <c r="V10" s="36" t="s">
         <v>69</v>
       </c>
       <c r="W10" s="4"/>
@@ -2045,7 +2063,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Z10" s="7"/>
+      <c r="Z10" s="36"/>
       <c r="AA10" s="7">
         <v>0.64444444444444438</v>
       </c>
@@ -2103,7 +2121,7 @@
       </c>
     </row>
     <row r="11" spans="1:40" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22">
+      <c r="A11" s="21">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -2126,23 +2144,23 @@
       <c r="H11" s="6">
         <v>0.4375</v>
       </c>
-      <c r="I11" s="30">
-        <v>0</v>
-      </c>
-      <c r="J11" s="30">
+      <c r="I11" s="29">
+        <v>0</v>
+      </c>
+      <c r="J11" s="29">
         <v>3</v>
       </c>
       <c r="K11" s="20">
         <f t="shared" si="2"/>
         <v>0.5625</v>
       </c>
-      <c r="L11" s="30">
+      <c r="L11" s="29">
         <v>2</v>
       </c>
-      <c r="M11" s="30">
+      <c r="M11" s="29">
         <v>0.5</v>
       </c>
-      <c r="N11" s="8" t="s">
+      <c r="N11" s="15" t="s">
         <v>56</v>
       </c>
       <c r="O11" s="20">
@@ -2153,7 +2171,7 @@
         <f t="shared" si="4"/>
         <v>0.66666666666666674</v>
       </c>
-      <c r="Q11" s="30">
+      <c r="Q11" s="29">
         <v>0.7</v>
       </c>
       <c r="R11" s="20">
@@ -2177,7 +2195,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Z11" s="7"/>
+      <c r="Z11" s="36"/>
       <c r="AA11" s="7">
         <v>0.77083333333333337</v>
       </c>
@@ -2235,43 +2253,43 @@
       </c>
     </row>
     <row r="12" spans="1:40" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="23">
+      <c r="A12" s="22">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="23">
         <v>46196</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="D12" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="24"/>
-      <c r="F12" s="26" t="s">
+      <c r="E12" s="23"/>
+      <c r="F12" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="G12" s="26" t="s">
+      <c r="G12" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="26">
         <v>0.4375</v>
       </c>
-      <c r="I12" s="31">
-        <v>0</v>
-      </c>
-      <c r="J12" s="31">
+      <c r="I12" s="30">
+        <v>0</v>
+      </c>
+      <c r="J12" s="30">
         <v>2</v>
       </c>
       <c r="K12" s="20">
         <f t="shared" si="2"/>
         <v>0.52083333333333337</v>
       </c>
-      <c r="L12" s="31">
+      <c r="L12" s="30">
         <v>6</v>
       </c>
-      <c r="M12" s="31">
+      <c r="M12" s="30">
         <v>0.5</v>
       </c>
       <c r="N12" s="8" t="s">
@@ -2285,85 +2303,85 @@
         <f t="shared" si="4"/>
         <v>0.79166666666666674</v>
       </c>
-      <c r="Q12" s="31">
+      <c r="Q12" s="30">
         <v>0.7</v>
       </c>
       <c r="R12" s="20">
         <f t="shared" si="5"/>
         <v>0.82083333333333341</v>
       </c>
-      <c r="S12" s="27">
+      <c r="S12" s="26">
         <v>0.82291666666666663</v>
       </c>
       <c r="T12" s="20">
         <f t="shared" si="6"/>
         <v>2.0833333333332149E-3</v>
       </c>
-      <c r="U12" s="28"/>
-      <c r="V12" s="28"/>
-      <c r="W12" s="26"/>
-      <c r="X12" s="28">
+      <c r="U12" s="27"/>
+      <c r="V12" s="27"/>
+      <c r="W12" s="25"/>
+      <c r="X12" s="27">
         <v>0.83333333333333337</v>
       </c>
-      <c r="Y12" s="28">
+      <c r="Y12" s="27">
         <f t="shared" si="0"/>
         <v>1.0416666666666741E-2</v>
       </c>
-      <c r="Z12" s="28" t="s">
+      <c r="Z12" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="AA12" s="28">
+      <c r="AA12" s="27">
         <v>0.64531249999999996</v>
       </c>
-      <c r="AB12" s="28">
+      <c r="AB12" s="27">
         <f>VLOOKUP(D12,Sheet2!J:K,2,0)</f>
         <v>2</v>
       </c>
-      <c r="AC12" s="28">
+      <c r="AC12" s="27">
         <f>VLOOKUP(D12,Sheet2!J:L,3,0)</f>
         <v>1</v>
       </c>
-      <c r="AD12" s="28">
+      <c r="AD12" s="27">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AE12" s="28">
+      <c r="AE12" s="27">
         <f t="shared" si="17"/>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="AF12" s="28">
+      <c r="AF12" s="27">
         <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
-      <c r="AG12" s="28">
+      <c r="AG12" s="27">
         <f t="shared" si="9"/>
         <v>8.6805555555550626E-5</v>
       </c>
-      <c r="AH12" s="28">
+      <c r="AH12" s="27">
         <f t="shared" si="10"/>
         <v>4.3402777777778084E-4</v>
       </c>
-      <c r="AI12" s="28">
+      <c r="AI12" s="27">
         <f t="shared" si="11"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="AJ12" s="28">
+      <c r="AJ12" s="27">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AK12" s="28">
+      <c r="AK12" s="27">
         <f t="shared" si="13"/>
         <v>0.20833333333333334</v>
       </c>
-      <c r="AL12" s="28">
+      <c r="AL12" s="27">
         <f t="shared" si="14"/>
         <v>0.35468749999999999</v>
       </c>
-      <c r="AM12" s="28">
+      <c r="AM12" s="27">
         <f t="shared" si="15"/>
         <v>0.64531249999999996</v>
       </c>
-      <c r="AN12" s="28">
+      <c r="AN12" s="27">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -3607,10 +3625,10 @@
       <c r="J3" t="s">
         <v>60</v>
       </c>
-      <c r="K3" s="32">
+      <c r="K3" s="31">
         <v>0.5</v>
       </c>
-      <c r="L3" s="32">
+      <c r="L3" s="31">
         <v>1</v>
       </c>
     </row>
@@ -3633,10 +3651,10 @@
       <c r="J4" t="s">
         <v>43</v>
       </c>
-      <c r="K4" s="32">
+      <c r="K4" s="31">
         <v>1</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="31">
         <v>1</v>
       </c>
     </row>
@@ -3656,10 +3674,10 @@
       <c r="J5" t="s">
         <v>67</v>
       </c>
-      <c r="K5" s="32">
+      <c r="K5" s="31">
         <v>2</v>
       </c>
-      <c r="L5" s="32">
+      <c r="L5" s="31">
         <v>1</v>
       </c>
     </row>
@@ -3676,10 +3694,10 @@
       <c r="J6" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="32">
+      <c r="K6" s="31">
         <v>3</v>
       </c>
-      <c r="L6" s="32">
+      <c r="L6" s="31">
         <v>1</v>
       </c>
     </row>
